--- a/АБК/Том СКУД АБК/Журнал входного контроля СКУД АБК.xlsx
+++ b/АБК/Том СКУД АБК/Журнал входного контроля СКУД АБК.xlsx
@@ -576,7 +576,7 @@
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Рабочая документация 16/1/26-СКУД-Р, лист 4; исполнительная документация 16/1/26-ИД-АБК, лист 4. Количество материалов — по АОСР № 1-СКУД-АБК, 2-СКУД-АБК; оборудование — по исполнительной документации.</t>
+          <t>Рабочая документация 16/1/26-СКУД-Р, лист 4; исполнительная документация 16/1/26-СКУД-ИД-АБК, лист 2. Спецификация 16/1/26-СКУД-ИД-АБК.СО. Количество материалов — по АОСР № 1-СКУД-АБК, 2-СКУД-АБК; оборудование — по исполнительной документации.</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="K25" s="11" t="inlineStr">
         <is>
-          <t>ИД лист 4</t>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="K26" s="11" t="inlineStr">
         <is>
-          <t>ИД лист 4</t>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="K27" s="11" t="inlineStr">
         <is>
-          <t>ИД лист 4</t>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="K28" s="11" t="inlineStr">
         <is>
-          <t>ИД лист 4</t>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="K29" s="11" t="inlineStr">
         <is>
-          <t>ИД лист 4</t>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="K30" s="11" t="inlineStr">
         <is>
-          <t>ИД лист 4</t>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>

--- a/АБК/Том СКУД АБК/Журнал входного контроля СКУД АБК.xlsx
+++ b/АБК/Том СКУД АБК/Журнал входного контроля СКУД АБК.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1462,49 +1462,102 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Батарея аккумуляторная 12 В 18 А·ч (в РИП-12, UG5), DT 12В 18Ач</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>Паспорт (руководство по эксплуатации) изготовителя</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>Внешний осмотр, маркировка, комплектность — без замечаний. Паспорт изготовителя в наличии (оригинал).</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>Соответствует. Допущено к применению</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>Иванчук М.В.</t>
+        </is>
+      </c>
+      <c r="K31" s="11" t="inlineStr">
+        <is>
+          <t>ИД лист 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>Ответственный за входной контроль (лицо, выполняющее работы)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>начальник отдела систем технической безопасности ООО «АльтЭн» Иванчук М.В.</t>
         </is>
       </c>
-      <c r="G33" s="14" t="inlineStr">
+      <c r="G34" s="14" t="inlineStr">
         <is>
           <t>____________________ (подпись)</t>
         </is>
       </c>
-      <c r="I33" s="14" t="inlineStr">
+      <c r="I34" s="14" t="inlineStr">
         <is>
           <t>«____» ____________ 2026 г.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="12" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>Представитель лица, осуществляющего строительство</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>руководитель проекта Белоногов И.Ю.</t>
         </is>
       </c>
-      <c r="G36" s="14" t="inlineStr">
+      <c r="G37" s="14" t="inlineStr">
         <is>
           <t>____________________ (подпись)</t>
         </is>
       </c>
-      <c r="I36" s="14" t="inlineStr">
+      <c r="I37" s="14" t="inlineStr">
         <is>
           <t>«____» ____________ 2026 г.</t>
         </is>
@@ -1513,23 +1566,23 @@
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="A15:K15"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="I37:K37"/>
     <mergeCell ref="A24:K24"/>
     <mergeCell ref="A11:K11"/>
-    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="A36:K36"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A6:K6"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="I33:K33"/>
     <mergeCell ref="A7:K7"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="G34:H34"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="G33:H33"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="I34:K34"/>
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A8:K8"/>
-    <mergeCell ref="A35:K35"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="I36:K36"/>
     <mergeCell ref="A10:K10"/>
     <mergeCell ref="A9:K9"/>
   </mergeCells>

--- a/АБК/Том СКУД АБК/Журнал входного контроля СКУД АБК.xlsx
+++ b/АБК/Том СКУД АБК/Журнал входного контроля СКУД АБК.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Болид</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ALer (ООО «ЭКСКОН»)</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Smartec</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Smartec</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
